--- a/backend/output_maquettes/MAQUETTE_A_AFFECTATION_GB.xlsx
+++ b/backend/output_maquettes/MAQUETTE_A_AFFECTATION_GB.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" min="1" max="1"/>
@@ -501,7 +501,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -551,7 +551,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -846,46 +846,46 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>11_1_</t>
+          <t>83_1_1</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Culture digitale (CM)</t>
+          <t>Biologie Animale et Végétale (TP) - GB-GEG S2 Gr 1</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>OUAARAB Aziz</t>
+          <t>------- (unknown)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>12_1_1</t>
+          <t>83_1_2</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Culture digitale (TD) - GB-GEG S2 Gr 1</t>
+          <t>Biologie Animale et Végétale (TP) - GB-GEG S2 Gr 2</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -896,21 +896,21 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>12_1_2</t>
+          <t>83_1_3</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Culture digitale (TD) - GB-GEG S2 Gr 2</t>
+          <t>Biologie Animale et Végétale (TP) - GB-GEG S2 Gr 3</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
@@ -921,21 +921,21 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>12_1_3</t>
+          <t>83_1_4</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Culture digitale (TD) - GB-GEG S2 Gr 3</t>
+          <t>Biologie Animale et Végétale (TP) - GB-GEG S2 Gr 4</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
@@ -946,21 +946,21 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>12_1_4</t>
+          <t>83_1_5</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Culture digitale (TD) - GB-GEG S2 Gr 4</t>
+          <t>Biologie Animale et Végétale (TP) - GB-GEG S2 Gr 5</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
@@ -971,21 +971,21 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>12_1_5</t>
+          <t>83_1_6</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Culture digitale (TD) - GB-GEG S2 Gr 5</t>
+          <t>Biologie Animale et Végétale (TP) - GB-GEG S2 Gr 6</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
@@ -996,17 +996,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>12_1_6</t>
+          <t>11_1_</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Culture digitale (TD) - GB-GEG S2 Gr 6</t>
+          <t>Culture digitale (CM)</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -1014,24 +1014,24 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>------- (unknown)</t>
+          <t>OUAARAB Aziz</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>5_1_</t>
+          <t>12_1_1</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Géodynamique externe (CM)</t>
+          <t>Culture digitale (TD) - GB-GEG S2 Gr 1</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
@@ -1039,24 +1039,24 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>IGMOULLAN Brahim</t>
+          <t>------- (unknown)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>6_1_1</t>
+          <t>12_1_2</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Géodynamique externe (TD) - GB-GEG S2 Gr 1</t>
+          <t>Culture digitale (TD) - GB-GEG S2 Gr 2</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -1071,17 +1071,17 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>6_1_2</t>
+          <t>12_1_3</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Géodynamique externe (TD) - GB-GEG S2 Gr 2</t>
+          <t>Culture digitale (TD) - GB-GEG S2 Gr 3</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -1096,17 +1096,17 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>6_1_3</t>
+          <t>12_1_4</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Géodynamique externe (TD) - GB-GEG S2 Gr 3</t>
+          <t>Culture digitale (TD) - GB-GEG S2 Gr 4</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
@@ -1121,17 +1121,17 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>6_1_4</t>
+          <t>12_1_5</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Géodynamique externe (TD) - GB-GEG S2 Gr 4</t>
+          <t>Culture digitale (TD) - GB-GEG S2 Gr 5</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
@@ -1146,17 +1146,17 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>6_1_5</t>
+          <t>12_1_6</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Géodynamique externe (TD) - GB-GEG S2 Gr 5</t>
+          <t>Culture digitale (TD) - GB-GEG S2 Gr 6</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
@@ -1171,17 +1171,17 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>6_1_6</t>
+          <t>5_1_</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Géodynamique externe (TD) - GB-GEG S2 Gr 6</t>
+          <t>Géodynamique externe (CM)</t>
         </is>
       </c>
       <c r="D32" s="3" t="n">
@@ -1189,24 +1189,24 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>------- (unknown)</t>
+          <t>IGMOULLAN Brahim</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>9_1_</t>
+          <t>6_1_1</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Langue Etrangère 2 (CM)</t>
+          <t>Géodynamique externe (TD) - GB-GEG S2 Gr 1</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
@@ -1214,24 +1214,24 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>SADOUK  Leila</t>
+          <t>------- (unknown)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>10_1_1</t>
+          <t>6_1_2</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Langue Etrangère 2 (TD) - GB-GEG S2 Gr 1</t>
+          <t>Géodynamique externe (TD) - GB-GEG S2 Gr 2</t>
         </is>
       </c>
       <c r="D34" s="3" t="n">
@@ -1246,17 +1246,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>10_1_2</t>
+          <t>6_1_3</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Langue Etrangère 2 (TD) - GB-GEG S2 Gr 2</t>
+          <t>Géodynamique externe (TD) - GB-GEG S2 Gr 3</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
@@ -1271,17 +1271,17 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>10_1_3</t>
+          <t>6_1_4</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Langue Etrangère 2 (TD) - GB-GEG S2 Gr 3</t>
+          <t>Géodynamique externe (TD) - GB-GEG S2 Gr 4</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
@@ -1296,17 +1296,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>10_1_4</t>
+          <t>6_1_5</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Langue Etrangère 2 (TD) - GB-GEG S2 Gr 4</t>
+          <t>Géodynamique externe (TD) - GB-GEG S2 Gr 5</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
@@ -1321,17 +1321,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>10_1_5</t>
+          <t>6_1_6</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Langue Etrangère 2 (TD) - GB-GEG S2 Gr 5</t>
+          <t>Géodynamique externe (TD) - GB-GEG S2 Gr 6</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">
@@ -1346,21 +1346,21 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>10_1_6</t>
+          <t>88_1_1</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Langue Etrangère 2 (TD) - GB-GEG S2 Gr 6</t>
+          <t>Géodynamique externe (TP) - GB-GEG S2 Gr 1</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
@@ -1371,46 +1371,46 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>47_1_</t>
+          <t>88_1_2</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Mécanique des Fluides et Transfert Thermique (CM)</t>
+          <t>Géodynamique externe (TP) - GB-GEG S2 Gr 2</t>
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>CHEHOUANI Hassan</t>
+          <t>------- (unknown)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>48_1_1</t>
+          <t>88_1_3</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Mécanique des Fluides et Transfert Thermique (TD) - GB-GEG S2 Gr 1</t>
+          <t>Géodynamique externe (TP) - GB-GEG S2 Gr 3</t>
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
@@ -1421,21 +1421,21 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>48_1_2</t>
+          <t>88_1_4</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Mécanique des Fluides et Transfert Thermique (TD) - GB-GEG S2 Gr 2</t>
+          <t>Géodynamique externe (TP) - GB-GEG S2 Gr 4</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
@@ -1446,21 +1446,21 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>48_1_3</t>
+          <t>88_1_5</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Mécanique des Fluides et Transfert Thermique (TD) - GB-GEG S2 Gr 3</t>
+          <t>Géodynamique externe (TP) - GB-GEG S2 Gr 5</t>
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
@@ -1471,21 +1471,21 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>48_1_4</t>
+          <t>88_1_6</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Mécanique des Fluides et Transfert Thermique (TD) - GB-GEG S2 Gr 4</t>
+          <t>Géodynamique externe (TP) - GB-GEG S2 Gr 6</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
@@ -1496,17 +1496,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>48_1_5</t>
+          <t>9_1_</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Mécanique des Fluides et Transfert Thermique (TD) - GB-GEG S2 Gr 5</t>
+          <t>Langue Etrangère 2 (CM)</t>
         </is>
       </c>
       <c r="D45" s="3" t="n">
@@ -1514,24 +1514,24 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>------- (unknown)</t>
+          <t>SADOUK  Leila</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>48_1_6</t>
+          <t>10_1_1</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Mécanique des Fluides et Transfert Thermique (TD) - GB-GEG S2 Gr 6</t>
+          <t>Langue Etrangère 2 (TD) - GB-GEG S2 Gr 1</t>
         </is>
       </c>
       <c r="D46" s="3" t="n">
@@ -1546,17 +1546,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>7_1_</t>
+          <t>10_1_2</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Réactivité Chimique (CM)</t>
+          <t>Langue Etrangère 2 (TD) - GB-GEG S2 Gr 2</t>
         </is>
       </c>
       <c r="D47" s="3" t="n">
@@ -1564,24 +1564,24 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>EL MAKHFOUK Mohammed</t>
+          <t>------- (unknown)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>8_1_1</t>
+          <t>10_1_3</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Réactivité Chimique (TD) - GB-GEG S2 Gr 1</t>
+          <t>Langue Etrangère 2 (TD) - GB-GEG S2 Gr 3</t>
         </is>
       </c>
       <c r="D48" s="3" t="n">
@@ -1596,17 +1596,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>8_1_2</t>
+          <t>10_1_4</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Réactivité Chimique (TD) - GB-GEG S2 Gr 2</t>
+          <t>Langue Etrangère 2 (TD) - GB-GEG S2 Gr 4</t>
         </is>
       </c>
       <c r="D49" s="3" t="n">
@@ -1621,17 +1621,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>8_1_3</t>
+          <t>10_1_5</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Réactivité Chimique (TD) - GB-GEG S2 Gr 3</t>
+          <t>Langue Etrangère 2 (TD) - GB-GEG S2 Gr 5</t>
         </is>
       </c>
       <c r="D50" s="3" t="n">
@@ -1646,17 +1646,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>8_1_4</t>
+          <t>10_1_6</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Réactivité Chimique (TD) - GB-GEG S2 Gr 4</t>
+          <t>Langue Etrangère 2 (TD) - GB-GEG S2 Gr 6</t>
         </is>
       </c>
       <c r="D51" s="3" t="n">
@@ -1671,17 +1671,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>8_1_5</t>
+          <t>47_1_</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Réactivité Chimique (TD) - GB-GEG S2 Gr 5</t>
+          <t>Mécanique des Fluides et Transfert Thermique (CM)</t>
         </is>
       </c>
       <c r="D52" s="3" t="n">
@@ -1689,24 +1689,24 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>------- (unknown)</t>
+          <t>CHEHOUANI Hassan</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>8_1_6</t>
+          <t>48_1_1</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>GB S2</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Réactivité Chimique (TD) - GB-GEG S2 Gr 6</t>
+          <t>Mécanique des Fluides et Transfert Thermique (TD) - GB-GEG S2 Gr 1</t>
         </is>
       </c>
       <c r="D53" s="3" t="n">
@@ -1721,17 +1721,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>39_9_</t>
+          <t>48_1_2</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>GB S4</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Analyse de Données (CM)</t>
+          <t>Mécanique des Fluides et Transfert Thermique (TD) - GB-GEG S2 Gr 2</t>
         </is>
       </c>
       <c r="D54" s="3" t="n">
@@ -1739,24 +1739,24 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>OUAARAB Aziz</t>
+          <t>------- (unknown)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>40_9_29</t>
+          <t>48_1_3</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>GB S4</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Analyse de Données (TD) - GB S4 Gr 1</t>
+          <t>Mécanique des Fluides et Transfert Thermique (TD) - GB-GEG S2 Gr 3</t>
         </is>
       </c>
       <c r="D55" s="3" t="n">
@@ -1771,17 +1771,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>71_9_</t>
+          <t>48_1_4</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>GB S4</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Biochimie Métabolique et Enzymologie (CM)</t>
+          <t>Mécanique des Fluides et Transfert Thermique (TD) - GB-GEG S2 Gr 4</t>
         </is>
       </c>
       <c r="D56" s="3" t="n">
@@ -1789,24 +1789,24 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>SEDDIQI Nadia</t>
+          <t>------- (unknown)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>72_9_29</t>
+          <t>48_1_5</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>GB S4</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Biochimie Métabolique et Enzymologie (TD) - GB S4 Gr 1</t>
+          <t>Mécanique des Fluides et Transfert Thermique (TD) - GB-GEG S2 Gr 5</t>
         </is>
       </c>
       <c r="D57" s="3" t="n">
@@ -1821,17 +1821,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>67_9_</t>
+          <t>48_1_6</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>GB S4</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Biologie Moléculaire et Génétique (CM)</t>
+          <t>Mécanique des Fluides et Transfert Thermique (TD) - GB-GEG S2 Gr 6</t>
         </is>
       </c>
       <c r="D58" s="3" t="n">
@@ -1839,24 +1839,24 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>TADLAOUI OUAFI AHmed</t>
+          <t>------- (unknown)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>68_9_29</t>
+          <t>7_1_</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>GB S4</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Biologie Moléculaire et Génétique (TD) - GB S4 Gr 1</t>
+          <t>Réactivité Chimique (CM)</t>
         </is>
       </c>
       <c r="D59" s="3" t="n">
@@ -1864,24 +1864,24 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>------- (unknown)</t>
+          <t>EL MAKHFOUK Mohammed</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>33_9_</t>
+          <t>8_1_1</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>GB S4</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Développement Personnel (CM)</t>
+          <t>Réactivité Chimique (TD) - GB-GEG S2 Gr 1</t>
         </is>
       </c>
       <c r="D60" s="3" t="n">
@@ -1889,24 +1889,24 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>KOURAD Hanane</t>
+          <t>------- (unknown)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>34_9_29</t>
+          <t>8_1_2</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>GB S4</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Développement Personnel (TD) - GB S4 Gr 1</t>
+          <t>Réactivité Chimique (TD) - GB-GEG S2 Gr 2</t>
         </is>
       </c>
       <c r="D61" s="3" t="n">
@@ -1921,17 +1921,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>31_9_</t>
+          <t>8_1_3</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>GB S4</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>LTC2 Français (CM)</t>
+          <t>Réactivité Chimique (TD) - GB-GEG S2 Gr 3</t>
         </is>
       </c>
       <c r="D62" s="3" t="n">
@@ -1939,24 +1939,24 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>El HASNAOUI Nadia</t>
+          <t>------- (unknown)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>32_9_29</t>
+          <t>8_1_4</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>GB S4</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>LTC2 Français (TD) - GB S4 Gr 1</t>
+          <t>Réactivité Chimique (TD) - GB-GEG S2 Gr 4</t>
         </is>
       </c>
       <c r="D63" s="3" t="n">
@@ -1971,17 +1971,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>69_9_</t>
+          <t>8_1_5</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>GB S4</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Méthodes d'analyse (CM)</t>
+          <t>Réactivité Chimique (TD) - GB-GEG S2 Gr 5</t>
         </is>
       </c>
       <c r="D64" s="3" t="n">
@@ -1989,24 +1989,24 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>MGHAZLI SAFAE</t>
+          <t>------- (unknown)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>70_9_29</t>
+          <t>8_1_6</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>GB S4</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Méthodes d'analyse (TD) - GB S4 Gr 1</t>
+          <t>Réactivité Chimique (TD) - GB-GEG S2 Gr 6</t>
         </is>
       </c>
       <c r="D65" s="3" t="n">
@@ -2021,48 +2021,773 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>73_9_</t>
+          <t>89_1_1</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>GB S4</t>
+          <t>GB-GEG S2</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Physiologie Animale et Végétale (CM)</t>
+          <t>Réactivité Chimique (TP) - GB-GEG S2 Gr 1</t>
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>ELHACHIMI Mly Youssef</t>
+          <t>------- (unknown)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
+          <t>89_1_2</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>GB-GEG S2</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Réactivité Chimique (TP) - GB-GEG S2 Gr 2</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>------- (unknown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>89_1_3</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>GB-GEG S2</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Réactivité Chimique (TP) - GB-GEG S2 Gr 3</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>------- (unknown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>89_1_4</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>GB-GEG S2</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Réactivité Chimique (TP) - GB-GEG S2 Gr 4</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>------- (unknown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>89_1_5</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>GB-GEG S2</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Réactivité Chimique (TP) - GB-GEG S2 Gr 5</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>------- (unknown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>89_1_6</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>GB-GEG S2</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Réactivité Chimique (TP) - GB-GEG S2 Gr 6</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>------- (unknown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>39_9_</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>GB S4</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Analyse de Données (CM)</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>OUAARAB Aziz</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>40_9_29</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>GB S4</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Analyse de Données (TD) - GB S4 Gr 1</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>------- (unknown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>40_9_35</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>GB S4</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Analyse de Données (TD) - GB S4 Gr 2</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>------- (unknown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>95_9_29</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>GB S4</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Analyse de Données (TP) - GB S4 Gr 1</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>------- (unknown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>95_9_35</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>GB S4</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Analyse de Données (TP) - GB S4 Gr 2</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>------- (unknown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>71_9_</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>GB S4</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Biochimie Métabolique et Enzymologie (CM)</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>SEDDIQI Nadia</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>72_9_29</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>GB S4</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>Biochimie Métabolique et Enzymologie (TD) - GB S4 Gr 1</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>------- (unknown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>72_9_35</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>GB S4</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>Biochimie Métabolique et Enzymologie (TD) - GB S4 Gr 2</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>------- (unknown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>90_9_29</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>GB S4</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>Biochimie Métabolique et Enzymologie (TP) - GB S4 Gr 1</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>------- (unknown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>90_9_35</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>GB S4</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Biochimie Métabolique et Enzymologie (TP) - GB S4 Gr 2</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>------- (unknown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>67_9_</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>GB S4</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>Biologie Moléculaire et Génétique (CM)</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>TADLAOUI OUAFI AHmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>68_9_29</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>GB S4</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Biologie Moléculaire et Génétique (TD) - GB S4 Gr 1</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>------- (unknown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>68_9_35</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>GB S4</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>Biologie Moléculaire et Génétique (TD) - GB S4 Gr 2</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>------- (unknown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>33_9_</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>GB S4</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>Développement Personnel (CM)</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>KOURAD Hanane</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>34_9_29</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>GB S4</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>Développement Personnel (TD) - GB S4 Gr 1</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>------- (unknown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>34_9_35</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>GB S4</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>Développement Personnel (TD) - GB S4 Gr 2</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>------- (unknown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>31_9_</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>GB S4</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>LTC2 Français (CM)</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>El HASNAOUI Nadia</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>32_9_29</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>GB S4</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>LTC2 Français (TD) - GB S4 Gr 1</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>------- (unknown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>32_9_35</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>GB S4</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>LTC2 Français (TD) - GB S4 Gr 2</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>------- (unknown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>69_9_</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>GB S4</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>Méthodes d'analyse (CM)</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>MGHAZLI SAFAE</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>70_9_29</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>GB S4</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>Méthodes d'analyse (TD) - GB S4 Gr 1</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>------- (unknown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>70_9_35</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>GB S4</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>Méthodes d'analyse (TD) - GB S4 Gr 2</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>------- (unknown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>73_9_</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>GB S4</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>Physiologie Animale et Végétale (CM)</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>ELHACHIMI Mly Youssef</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
           <t>74_9_29</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B95" s="3" t="inlineStr">
         <is>
           <t>GB S4</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C95" s="3" t="inlineStr">
         <is>
           <t>Physiologie Animale et Végétale (TD) - GB S4 Gr 1</t>
         </is>
       </c>
-      <c r="D67" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
+      <c r="D95" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>------- (unknown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>74_9_35</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>GB S4</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>Physiologie Animale et Végétale (TD) - GB S4 Gr 2</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
         <is>
           <t>------- (unknown)</t>
         </is>
